--- a/research_evaluation_20261030/results/SUMMARY_TABLES.xlsx
+++ b/research_evaluation_20261030/results/SUMMARY_TABLES.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,21 +445,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Answer labels: manual reading by one author against reference answers, tuples and gold evidence (not independent).</t>
+          <t>Gold questions, reference answers, tuples and evidence regions: written by Claude from the extracted text, light text check, accepted by the project owner (frozen_20261030/gold_questions.jsonl).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Not completed: P047-P050 (generator offline), P007 (withheld by citation check); see sheet error_cases.</t>
+          <t>Answer labels: one LLM-assisted reading pass (Claude) against reference answers, tuples and gold evidence; not independent (column grader of sheet manual_grades).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Not used: mainflow_20261030/judgments.jsonl and report/ (automatic Qwen judge stopped after 14 of 100 answers).</t>
+          <t>Text-only main flow: all 50 answered; P047-P050 and P007 come from a second run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Image policy: 45 of 50 answered; not completed: P047-P050 (generator offline), P007 (withheld by citation check); see sheet error_cases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>In summary_mean_sd, *_of_claims rows are shares of all claims (used in the paper); the rows without that suffix are means over questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Not used and not included in this repository: mainflow_20261030/judgments.jsonl and report/ (automatic Qwen judge stopped after 14 of 100 answers).</t>
         </is>
       </c>
     </row>
@@ -474,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,7 +604,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no (mean over questions; the paper uses the share of claims)</t>
         </is>
       </c>
     </row>
@@ -609,7 +630,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no (mean over questions; the paper uses the share of claims)</t>
         </is>
       </c>
     </row>
@@ -829,14 +850,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>count_correct</t>
+          <t>attribute_leakage_rate_of_claims</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>0.051</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -852,14 +873,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>count_partial</t>
+          <t>citation_faithfulness_of_claims</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>0.888</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -875,11 +896,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>count_wrong</t>
+          <t>count_correct</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E16" t="n">
         <v>50</v>
@@ -898,11 +919,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>count_no_answer</t>
+          <t>count_partial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E17" t="n">
         <v>50</v>
@@ -916,52 +937,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>image_policy</t>
+          <t>text_only</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>answer_accuracy</t>
+          <t>count_wrong</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.744</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.379</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>no (zero-shot VLM; kept for the record)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>image_policy</t>
+          <t>text_only</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>strict_accuracy</t>
+          <t>count_no_answer</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.484</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>no (zero-shot VLM; kept for the record)</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -973,14 +988,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>attribute_leakage_rate</t>
+          <t>answer_accuracy</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.074</v>
+        <v>0.744</v>
       </c>
       <c r="D20" t="n">
-        <v>0.206</v>
+        <v>0.379</v>
       </c>
       <c r="E20" t="n">
         <v>45</v>
@@ -999,14 +1014,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>citation_faithfulness</t>
+          <t>strict_accuracy</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.826</v>
+        <v>0.644</v>
       </c>
       <c r="D21" t="n">
-        <v>0.32</v>
+        <v>0.484</v>
       </c>
       <c r="E21" t="n">
         <v>45</v>
@@ -1025,17 +1040,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>key_value_recall</t>
+          <t>attribute_leakage_rate</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.775</v>
+        <v>0.074</v>
       </c>
       <c r="D22" t="n">
-        <v>0.368</v>
+        <v>0.206</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1051,14 +1066,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>evidence_recall_at_10</t>
+          <t>citation_faithfulness</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.919</v>
+        <v>0.826</v>
       </c>
       <c r="D23" t="n">
-        <v>0.221</v>
+        <v>0.32</v>
       </c>
       <c r="E23" t="n">
         <v>45</v>
@@ -1077,17 +1092,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>evidence_precision_at_10</t>
+          <t>key_value_recall</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.12</v>
+        <v>0.775</v>
       </c>
       <c r="D24" t="n">
-        <v>0.055</v>
+        <v>0.368</v>
       </c>
       <c r="E24" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1103,14 +1118,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>required_evidence_recall</t>
+          <t>evidence_recall_at_10</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.956</v>
+        <v>0.919</v>
       </c>
       <c r="D25" t="n">
-        <v>0.179</v>
+        <v>0.221</v>
       </c>
       <c r="E25" t="n">
         <v>45</v>
@@ -1129,14 +1144,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>citation_precision</t>
+          <t>evidence_precision_at_10</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.741</v>
+        <v>0.12</v>
       </c>
       <c r="D26" t="n">
-        <v>0.382</v>
+        <v>0.055</v>
       </c>
       <c r="E26" t="n">
         <v>45</v>
@@ -1155,14 +1170,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>citation_recall</t>
+          <t>required_evidence_recall</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.737</v>
+        <v>0.956</v>
       </c>
       <c r="D27" t="n">
-        <v>0.385</v>
+        <v>0.179</v>
       </c>
       <c r="E27" t="n">
         <v>45</v>
@@ -1181,18 +1196,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>count_correct</t>
+          <t>citation_precision</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>29</v>
+        <v>0.741</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.382</v>
       </c>
       <c r="E28" t="n">
         <v>45</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no (zero-shot VLM; kept for the record)</t>
         </is>
       </c>
     </row>
@@ -1204,18 +1222,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>count_partial</t>
+          <t>citation_recall</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>0.737</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.385</v>
       </c>
       <c r="E29" t="n">
         <v>45</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>no (zero-shot VLM; kept for the record)</t>
         </is>
       </c>
     </row>
@@ -1227,14 +1248,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>count_wrong</t>
+          <t>attribute_leakage_rate_of_claims</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7</v>
+        <v>0.082</v>
       </c>
       <c r="E30" t="n">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,16 +1271,108 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>citation_faithfulness_of_claims</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E31" t="n">
+        <v>85</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>image_policy</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>count_correct</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>29</v>
+      </c>
+      <c r="E32" t="n">
+        <v>45</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>image_policy</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>count_partial</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>9</v>
+      </c>
+      <c r="E33" t="n">
+        <v>45</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>image_policy</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>count_wrong</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>45</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>image_policy</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>count_no_answer</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C35" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E35" t="n">
         <v>45</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -3977,12 +4090,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>accuracy</t>
+          <t>strict_accuracy</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>partial_credit</t>
+          <t>answer_accuracy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
